--- a/reports/pdf_rolling5_20260730.xlsx
+++ b/reports/pdf_rolling5_20260730.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-07-23 ~ 2026-07-30  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-07-23 ~ 2026-07-30  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,706억   ·   현금 292억(8.2%)      오늘 2026-07-30  vs  5일전 2026-07-23      매수 7종목  /  매도 12종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,438억   ·   현금 294억(8.2%)      오늘 2026-07-30  vs  5일전 2026-07-23      매수 7종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>211</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>829085465</v>
+        <v>835778385</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-171</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-11065803300</v>
+        <v>-11155133700</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>47</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1020036300</v>
+        <v>1028270700</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-45</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1114875000</v>
+        <v>-1123875000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>32</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1441310400</v>
+        <v>1452945600</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-42</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-531512940</v>
+        <v>-535803660</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>20</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>705592000</v>
+        <v>711288000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-32</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1595113600</v>
+        <v>-1607990400</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>318111000</v>
+        <v>320679000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-25</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-351557250</v>
+        <v>-354395250</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>305921700</v>
+        <v>308391300</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-19</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-667488050</v>
+        <v>-672876450</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>271930400</v>
+        <v>274125600</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-13</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1212290300</v>
+        <v>-1222076700</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>-11</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-600645100</v>
+        <v>-605493900</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>-8</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-181154800</v>
+        <v>-182617200</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1032,23 +1032,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-575275500</v>
+        <v>-570928500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.15%→0.88%</t>
+          <t>8.29%→7.59%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>30→25</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>
@@ -1060,23 +1060,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-566356500</v>
+        <v>-336663000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>8.29%→7.59%</t>
+          <t>0.46%→0.41%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>
@@ -1088,30 +1088,30 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-333967000</v>
+        <v>-579919500</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.41%</t>
+          <t>1.15%→0.88%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>30→25</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,347억   ·   현금 26억(0.8%)      오늘 2026-07-30  vs  5일전 2026-07-23      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,104억   ·   현금 26억(0.8%)      오늘 2026-07-30  vs  5일전 2026-07-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1133,528 +1133,519 @@
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
-      <c r="H22" s="20" t="n"/>
-      <c r="I22" s="20" t="n"/>
-      <c r="J22" s="20" t="n"/>
-      <c r="K22" s="20" t="n"/>
-    </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="n"/>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="20" t="n"/>
-      <c r="G24" s="20" t="n"/>
-      <c r="H24" s="20" t="n"/>
-      <c r="I24" s="20" t="n"/>
-      <c r="J24" s="20" t="n"/>
-      <c r="K24" s="20" t="n"/>
-    </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 239억   ·   현금 14억(5.7%)      오늘 2026-07-30  vs  5일전 2026-07-23      매수 9종목  /  매도 9종목</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 1,929억   ·   현금 68억(3.5%)      오늘 2026-07-30  vs  5일전 2026-07-23      매수 5종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>83</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>1635548200</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>1.54%→2.41%</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>150→233</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>코미코  (편출)</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-4949087000</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>2.10%→0.00%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>110→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>에코프로</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>1439596600</v>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>1.71%→2.61%</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>76→107</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>-70</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>-5512689000</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>8.69%→4.96%</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>190→120</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="8" t="n"/>
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>325139100</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>0.34%→0.34%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>25→51</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>오킨스전자</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>-296083970</v>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>0.36%→0.16%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>99→50</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>4282135000</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>2.35%→5.32%</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>30→52</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="17" t="n"/>
+      <c r="J28" s="17" t="n"/>
+      <c r="K28" s="17" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>심텍홀딩스</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>14065320</v>
+        <v>3394014000</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>0.46%→0.54%</t>
+          <t>2.24%→4.16%</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>485→547</t>
-        </is>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>코미코  (편출)</t>
-        </is>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>-152</v>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v>-628428800</v>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>2.64%→0.00%</t>
-        </is>
-      </c>
-      <c r="K29" s="13" t="inlineStr">
-        <is>
-          <t>152→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>에프앤가이드</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="n">
-        <v>49</v>
-      </c>
-      <c r="C30" s="11" t="n">
-        <v>63419720</v>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>3.11%→3.48%</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>573→622</t>
-        </is>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>씨에스베어링</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>-139</v>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v>-35811960</v>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>2.96%→2.89%</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="inlineStr">
-        <is>
-          <t>2,736→2,597</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>RF머트리얼즈</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="n">
-        <v>33</v>
-      </c>
-      <c r="C31" s="11" t="n">
-        <v>52417200</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>0.22%→0.45%</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>33→66</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="n">
-        <v>-81</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>-203455800</v>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>7.88%→7.23%</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="inlineStr">
-        <is>
-          <t>748→667</t>
-        </is>
-      </c>
+          <t>16→28</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="17" t="n"/>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,829억   ·   현금 55억(3.0%)      오늘 2026-07-30  vs  5일전 2026-07-23      매수 4종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>브이엠</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="C32" s="11" t="n">
-        <v>129070800</v>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>2.83%→3.47%</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>141→168</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>코오롱티슈진  (편출)</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>-77</v>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v>-85205120</v>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>0.36%→0.00%</t>
-        </is>
-      </c>
-      <c r="K32" s="13" t="inlineStr">
-        <is>
-          <t>77→0</t>
-        </is>
-      </c>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>알멕</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="C33" s="11" t="n">
-        <v>23267400</v>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>0.74%→0.86%</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>98→111</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>한중엔시에스</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>-30</v>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v>-62814000</v>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>3.21%→3.03%</t>
-        </is>
-      </c>
-      <c r="K33" s="13" t="inlineStr">
-        <is>
-          <t>365→335</t>
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
-        <v>12</v>
+        <v>328</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>111355200</v>
+        <v>6913879200</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>2.61%→3.16%</t>
+          <t>3.05%→6.81%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>67→79</t>
+          <t>250→578</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-11</v>
+        <v>-246</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-43137600</v>
+        <v>-14745240000</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>2.45%→2.34%</t>
+          <t>14.82%→8.34%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>149→138</t>
+          <t>495→249</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="B35" s="11" t="n">
-        <v>9</v>
+        <v>116</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>64432800</v>
+        <v>1879252200</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>2.61%→2.97%</t>
+          <t>3.07%→3.73%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>87→96</t>
+          <t>296→412</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-33744000</v>
+        <v>-3447549000</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>0.67%→0.55%</t>
+          <t>9.66%→9.08%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>38→30</t>
+          <t>40→33</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>47690000</v>
+        <v>2224806300</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>2.68%→2.96%</t>
+          <t>6.31%→7.33%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>67→72</t>
-        </is>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>리가켐바이오  (편출)</t>
-        </is>
-      </c>
-      <c r="H36" s="15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I36" s="15" t="n">
-        <v>-48199200</v>
-      </c>
-      <c r="J36" s="16" t="inlineStr">
-        <is>
-          <t>0.20%→0.00%</t>
-        </is>
-      </c>
-      <c r="K36" s="13" t="inlineStr">
-        <is>
-          <t>7→0</t>
-        </is>
-      </c>
+          <t>348→419</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="n"/>
+      <c r="H36" s="17" t="n"/>
+      <c r="I36" s="17" t="n"/>
+      <c r="J36" s="17" t="n"/>
+      <c r="K36" s="17" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>30400000</v>
+        <v>3856972500</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>0.99%→1.15%</t>
+          <t>10.33%→13.66%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>31→35</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>알테오젠</t>
-        </is>
-      </c>
-      <c r="H37" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I37" s="15" t="n">
-        <v>-67602000</v>
-      </c>
-      <c r="J37" s="16" t="inlineStr">
-        <is>
-          <t>1.89%→1.65%</t>
-        </is>
-      </c>
-      <c r="K37" s="13" t="inlineStr">
-        <is>
-          <t>20→17</t>
-        </is>
-      </c>
+          <t>219→260</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="n"/>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="17" t="n"/>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 454억   ·   현금 20억(4.5%)      오늘 2026-07-30  vs  5일전 2026-07-23      매수 4종목  /  매도 7종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 218억   ·   현금 14억(6.3%)      오늘 2026-07-30  vs  5일전 2026-07-23      매수 9종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>
@@ -1743,298 +1734,787 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>심텍홀딩스</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>503645400</v>
+        <v>12604600</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>5.07%→5.64%</t>
+          <t>0.45%→0.53%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>184→235</t>
+          <t>485→547</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>리센스메디컬  (편출)</t>
+          <t>코미코  (편출)</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-607</v>
+        <v>-152</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-746980270</v>
+        <v>-628428800</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>1.67%→0.00%</t>
+          <t>2.88%→0.00%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>607→0</t>
+          <t>152→0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>펩트론</t>
+          <t>에프앤가이드</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>147477000</v>
+        <v>54891760</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>1.57%→2.58%</t>
+          <t>2.94%→3.30%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>62→72</t>
+          <t>573→622</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>큐리오시스  (편출)</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-593</v>
+        <v>-139</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-672224800</v>
+        <v>-33646340</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>1.50%→0.00%</t>
+          <t>3.04%→2.98%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>593→0</t>
+          <t>2,736→2,597</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>휴젤</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>225139500</v>
+        <v>45520200</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>4.32%→5.41%</t>
+          <t>0.21%→0.43%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>80→89</t>
+          <t>33→66</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>큐라클</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-518</v>
+        <v>-81</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-410478740</v>
+        <v>-181909800</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>1.25%→0.19%</t>
+          <t>7.71%→7.09%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>617→99</t>
+          <t>748→667</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>117169200</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>2.81%→3.45%</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>141→168</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>코오롱티슈진  (편출)</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>-77</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>-77246400</v>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>0.35%→0.00%</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>77→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>알멕</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>21291400</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>0.74%→0.86%</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>98→111</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>-57000000</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>3.18%→3.01%</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>365→335</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>104241600</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>2.67%→3.25%</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>67→79</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>-39501000</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>2.45%→2.35%</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>149→138</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>56156400</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>2.49%→2.84%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>87→96</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-29579200</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>0.64%→0.53%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>38→30</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>43662000</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>2.68%→2.98%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>67→72</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오  (편출)</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-44102800</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>0.20%→0.00%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>7→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>27968000</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>0.99%→1.16%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>31→35</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-64410000</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>1.97%→1.73%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>20→17</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 433억   ·   현금 20억(4.5%)      오늘 2026-07-30  vs  5일전 2026-07-23      매수 4종목  /  매도 7종목</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="8" t="n"/>
+      <c r="J53" s="8" t="n"/>
+      <c r="K53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>508266000</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>5.07%→5.64%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>184→235</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>리센스메디컬  (편출)</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-607</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-753833300</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>1.67%→0.00%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>607→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>펩트론</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>148830000</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>1.57%→2.58%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>62→72</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>큐리오시스  (편출)</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-593</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-678392000</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>1.50%→0.00%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>593→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>휴젤</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>227205000</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>4.32%→5.41%</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>80→89</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>큐라클</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-518</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-414244600</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>1.25%→0.19%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>617→99</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
           <t>삼성바이오로직스  (신규)</t>
         </is>
       </c>
-      <c r="B45" s="11" t="n">
+      <c r="B58" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>1128477000</v>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="C58" s="11" t="n">
+        <v>1138830000</v>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>0.00%→2.74%</t>
         </is>
       </c>
-      <c r="E45" s="13" t="inlineStr">
+      <c r="E58" s="13" t="inlineStr">
         <is>
           <t>0→7</t>
         </is>
       </c>
-      <c r="G45" s="14" t="inlineStr">
+      <c r="G58" s="14" t="inlineStr">
         <is>
           <t>코오롱티슈진  (편출)</t>
         </is>
       </c>
-      <c r="H45" s="15" t="n">
+      <c r="H58" s="15" t="n">
         <v>-104</v>
       </c>
-      <c r="I45" s="15" t="n">
-        <v>-340646800</v>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
+      <c r="I58" s="15" t="n">
+        <v>-343772000</v>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
         <is>
           <t>0.76%→0.00%</t>
         </is>
       </c>
-      <c r="K45" s="13" t="inlineStr">
+      <c r="K58" s="13" t="inlineStr">
         <is>
           <t>104→0</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="17" t="n"/>
-      <c r="B46" s="17" t="n"/>
-      <c r="C46" s="17" t="n"/>
-      <c r="D46" s="17" t="n"/>
-      <c r="E46" s="17" t="n"/>
-      <c r="G46" s="14" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="17" t="n"/>
+      <c r="B59" s="17" t="n"/>
+      <c r="C59" s="17" t="n"/>
+      <c r="D59" s="17" t="n"/>
+      <c r="E59" s="17" t="n"/>
+      <c r="G59" s="14" t="inlineStr">
         <is>
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="H46" s="15" t="n">
+      <c r="H59" s="15" t="n">
         <v>-28</v>
       </c>
-      <c r="I46" s="15" t="n">
-        <v>-549360000</v>
-      </c>
-      <c r="J46" s="16" t="inlineStr">
+      <c r="I59" s="15" t="n">
+        <v>-554400000</v>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
         <is>
           <t>9.33%→9.39%</t>
         </is>
       </c>
-      <c r="K46" s="13" t="inlineStr">
+      <c r="K59" s="13" t="inlineStr">
         <is>
           <t>225→197</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="17" t="n"/>
-      <c r="B47" s="17" t="n"/>
-      <c r="C47" s="17" t="n"/>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="17" t="n"/>
-      <c r="G47" s="14" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="17" t="n"/>
+      <c r="B60" s="17" t="n"/>
+      <c r="C60" s="17" t="n"/>
+      <c r="D60" s="17" t="n"/>
+      <c r="E60" s="17" t="n"/>
+      <c r="G60" s="14" t="inlineStr">
         <is>
           <t>올릭스</t>
         </is>
       </c>
-      <c r="H47" s="15" t="n">
+      <c r="H60" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I47" s="15" t="n">
-        <v>-153853500</v>
-      </c>
-      <c r="J47" s="16" t="inlineStr">
+      <c r="I60" s="15" t="n">
+        <v>-155265000</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
         <is>
           <t>8.54%→8.10%</t>
         </is>
       </c>
-      <c r="K47" s="13" t="inlineStr">
+      <c r="K60" s="13" t="inlineStr">
         <is>
           <t>340→325</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="17" t="n"/>
-      <c r="B48" s="17" t="n"/>
-      <c r="C48" s="17" t="n"/>
-      <c r="D48" s="17" t="n"/>
-      <c r="E48" s="17" t="n"/>
-      <c r="G48" s="14" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="17" t="n"/>
+      <c r="B61" s="17" t="n"/>
+      <c r="C61" s="17" t="n"/>
+      <c r="D61" s="17" t="n"/>
+      <c r="E61" s="17" t="n"/>
+      <c r="G61" s="14" t="inlineStr">
         <is>
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="H48" s="15" t="n">
+      <c r="H61" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I48" s="15" t="n">
-        <v>-400302500</v>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
+      <c r="I61" s="15" t="n">
+        <v>-403975000</v>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
         <is>
           <t>9.41%→9.80%</t>
         </is>
       </c>
-      <c r="K48" s="13" t="inlineStr">
+      <c r="K61" s="13" t="inlineStr">
         <is>
           <t>144→131</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="19" customHeight="1">
-      <c r="A50" s="19" t="inlineStr">
+    <row r="63" ht="19" customHeight="1">
+      <c r="A63" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B50" s="20" t="n"/>
-      <c r="C50" s="20" t="n"/>
-      <c r="D50" s="20" t="n"/>
-      <c r="E50" s="20" t="n"/>
-      <c r="F50" s="20" t="n"/>
-      <c r="G50" s="20" t="n"/>
-      <c r="H50" s="20" t="n"/>
-      <c r="I50" s="20" t="n"/>
-      <c r="J50" s="20" t="n"/>
-      <c r="K50" s="20" t="n"/>
+      <c r="B63" s="20" t="n"/>
+      <c r="C63" s="20" t="n"/>
+      <c r="D63" s="20" t="n"/>
+      <c r="E63" s="20" t="n"/>
+      <c r="F63" s="20" t="n"/>
+      <c r="G63" s="20" t="n"/>
+      <c r="H63" s="20" t="n"/>
+      <c r="I63" s="20" t="n"/>
+      <c r="J63" s="20" t="n"/>
+      <c r="K63" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="20">
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="G23:K23"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G53:K53"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A22:K22"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A50:K50"/>
-    <mergeCell ref="A3:K3"/>
     <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A39:K39"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G32:K32"/>
     <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A63:K63"/>
+    <mergeCell ref="A52:K52"/>
     <mergeCell ref="A40:E40"/>
-    <mergeCell ref="G27:K27"/>
-    <mergeCell ref="A1:K1"/>
     <mergeCell ref="G40:K40"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260730.xlsx
+++ b/reports/pdf_rolling5_20260730.xlsx
@@ -1032,23 +1032,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-570928500</v>
+        <v>-336663000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>8.29%→7.59%</t>
+          <t>0.46%→0.41%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>
@@ -1060,23 +1060,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-336663000</v>
+        <v>-570928500</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.41%</t>
+          <t>8.29%→7.59%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260730.xlsx
+++ b/reports/pdf_rolling5_20260730.xlsx
@@ -1032,23 +1032,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-336663000</v>
+        <v>-570928500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.41%</t>
+          <t>8.29%→7.59%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>
@@ -1060,23 +1060,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-570928500</v>
+        <v>-336663000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>8.29%→7.59%</t>
+          <t>0.46%→0.41%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260730.xlsx
+++ b/reports/pdf_rolling5_20260730.xlsx
@@ -1032,23 +1032,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-570928500</v>
+        <v>-579919500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>8.29%→7.59%</t>
+          <t>1.15%→0.88%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>30→25</t>
         </is>
       </c>
     </row>
@@ -1088,23 +1088,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-579919500</v>
+        <v>-570928500</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.15%→0.88%</t>
+          <t>8.29%→7.59%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>30→25</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>
